--- a/examples/ejercicio-resuelto.xlsx
+++ b/examples/ejercicio-resuelto.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2539" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2773" uniqueCount="231">
   <si>
     <t>INS#</t>
   </si>
@@ -298,6 +298,42 @@
     <t>0x000</t>
   </si>
   <si>
+    <t>I2</t>
+  </si>
+  <si>
+    <t>I3</t>
+  </si>
+  <si>
+    <t>I4</t>
+  </si>
+  <si>
+    <t>I5</t>
+  </si>
+  <si>
+    <t>I6</t>
+  </si>
+  <si>
+    <t>I7</t>
+  </si>
+  <si>
+    <t>I8</t>
+  </si>
+  <si>
+    <t>I9</t>
+  </si>
+  <si>
+    <t>I10</t>
+  </si>
+  <si>
+    <t>I11</t>
+  </si>
+  <si>
+    <t>I12</t>
+  </si>
+  <si>
+    <t>I13</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
@@ -506,6 +542,12 @@
   </si>
   <si>
     <t>Trae el bloque 0x0028-0x002F a L8</t>
+  </si>
+  <si>
+    <t>I0</t>
+  </si>
+  <si>
+    <t>I1</t>
   </si>
   <si>
     <t>0x0001</t>
@@ -4981,11 +5023,15 @@
       <c r="D52" s="21">
         <v>1</v>
       </c>
-      <c r="E52" s="21"/>
+      <c r="E52" s="21" t="s">
+        <v>92</v>
+      </c>
       <c r="F52" s="21"/>
       <c r="G52" s="21"/>
       <c r="H52" s="21"/>
-      <c r="I52" s="21"/>
+      <c r="I52" s="21" t="s">
+        <v>93</v>
+      </c>
       <c r="J52" s="21"/>
       <c r="K52" s="21"/>
       <c r="L52" s="21"/>
@@ -5003,11 +5049,15 @@
       <c r="D53" s="21">
         <v>1</v>
       </c>
-      <c r="E53" s="21"/>
+      <c r="E53" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="F53" s="21"/>
       <c r="G53" s="21"/>
       <c r="H53" s="21"/>
-      <c r="I53" s="21"/>
+      <c r="I53" s="21" t="s">
+        <v>95</v>
+      </c>
       <c r="J53" s="21"/>
       <c r="K53" s="21"/>
       <c r="L53" s="21"/>
@@ -5025,11 +5075,15 @@
       <c r="D54" s="21">
         <v>1</v>
       </c>
-      <c r="E54" s="21"/>
+      <c r="E54" s="21" t="s">
+        <v>96</v>
+      </c>
       <c r="F54" s="21"/>
       <c r="G54" s="21"/>
       <c r="H54" s="21"/>
-      <c r="I54" s="21"/>
+      <c r="I54" s="21" t="s">
+        <v>97</v>
+      </c>
       <c r="J54" s="21"/>
       <c r="K54" s="21"/>
       <c r="L54" s="21"/>
@@ -5047,11 +5101,15 @@
       <c r="D55" s="21">
         <v>1</v>
       </c>
-      <c r="E55" s="21"/>
+      <c r="E55" s="21" t="s">
+        <v>98</v>
+      </c>
       <c r="F55" s="21"/>
       <c r="G55" s="21"/>
       <c r="H55" s="21"/>
-      <c r="I55" s="21"/>
+      <c r="I55" s="21" t="s">
+        <v>99</v>
+      </c>
       <c r="J55" s="21"/>
       <c r="K55" s="21"/>
       <c r="L55" s="21"/>
@@ -5069,11 +5127,15 @@
       <c r="D56" s="21">
         <v>1</v>
       </c>
-      <c r="E56" s="21"/>
+      <c r="E56" s="21" t="s">
+        <v>100</v>
+      </c>
       <c r="F56" s="21"/>
       <c r="G56" s="21"/>
       <c r="H56" s="21"/>
-      <c r="I56" s="21"/>
+      <c r="I56" s="21" t="s">
+        <v>101</v>
+      </c>
       <c r="J56" s="21"/>
       <c r="K56" s="21"/>
       <c r="L56" s="21"/>
@@ -5091,11 +5153,15 @@
       <c r="D57" s="21">
         <v>1</v>
       </c>
-      <c r="E57" s="21"/>
+      <c r="E57" s="21" t="s">
+        <v>102</v>
+      </c>
       <c r="F57" s="21"/>
       <c r="G57" s="21"/>
       <c r="H57" s="21"/>
-      <c r="I57" s="21"/>
+      <c r="I57" s="21" t="s">
+        <v>103</v>
+      </c>
       <c r="J57" s="21"/>
       <c r="K57" s="21"/>
       <c r="L57" s="21"/>
@@ -5156,7 +5222,7 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="21" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="B61" s="21"/>
       <c r="C61" s="21"/>
@@ -5174,7 +5240,7 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="21" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B62" s="21"/>
       <c r="C62" s="21"/>
@@ -5192,7 +5258,7 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="21" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B63" s="21"/>
       <c r="C63" s="21"/>
@@ -5228,7 +5294,7 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="21" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="B65" s="21"/>
       <c r="C65" s="21"/>
@@ -5246,7 +5312,7 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="21" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="B66" s="21"/>
       <c r="C66" s="21"/>
@@ -5264,21 +5330,21 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="20" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="B69" s="20" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="C69" s="20" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="22" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B70" s="22" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C70" s="22">
         <v>4104</v>
@@ -5286,10 +5352,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="22" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B71" s="22" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C71" s="22">
         <v>8200</v>
@@ -5297,10 +5363,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="22" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="B72" s="22" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="C72" s="22">
         <v>8328</v>
@@ -5308,7 +5374,7 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="22" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B73" s="22" t="s">
         <v>13</v>
@@ -5319,10 +5385,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="22" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B74" s="22" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C74" s="22">
         <v>34</v>
@@ -5330,10 +5396,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="B75" s="22" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="C75" s="22">
         <v>512</v>
@@ -5341,10 +5407,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="B76" s="22" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C76" s="22">
         <v>546</v>
@@ -5405,36 +5471,36 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="28" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="29" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="29" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="29" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="B5" s="29">
         <v>8</v>
@@ -5442,7 +5508,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="B6" s="29">
         <v>16</v>
@@ -5450,31 +5516,31 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="29" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="29" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B10" s="29" t="s">
         <v>13</v>
@@ -5482,13 +5548,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="B12" s="30" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="D12" s="32" t="s">
         <v>5</v>
@@ -5496,7 +5562,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="29" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="B13" s="33">
         <v>9</v>
@@ -5510,7 +5576,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="B14" s="33">
         <v>10</v>
@@ -5524,7 +5590,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="29" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="B15" s="33">
         <v>11</v>
@@ -5538,7 +5604,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="29" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="B16" s="33">
         <v>13</v>
@@ -5552,30 +5618,30 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="D18" s="34" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="F18" s="34" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="G18" s="34" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="29" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="B19" s="33">
         <v>29</v>
@@ -5598,7 +5664,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="B20" s="33">
         <v>29</v>
@@ -5621,7 +5687,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="29" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="B21" s="33">
         <v>29</v>
@@ -5644,7 +5710,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="29" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="B22" s="33">
         <v>29</v>
@@ -5667,18 +5733,18 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="24" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -5837,12 +5903,12 @@
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="28" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="24" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="B42" s="24" t="s">
         <v>77</v>
@@ -6426,7 +6492,7 @@
         <v>32</v>
       </c>
       <c r="AA6" s="11" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
@@ -6692,7 +6758,7 @@
         <v>51</v>
       </c>
       <c r="AA10" s="11" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
@@ -6792,7 +6858,7 @@
         <v>26</v>
       </c>
       <c r="AA11" s="19" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
@@ -6994,7 +7060,7 @@
         <v>17</v>
       </c>
       <c r="AA13" s="19" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
@@ -7096,7 +7162,7 @@
         <v>63</v>
       </c>
       <c r="AA14" s="11" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
@@ -7320,7 +7386,7 @@
         <v>14</v>
       </c>
       <c r="X17" s="18" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="Y17" s="18" t="s">
         <v>15</v>
@@ -7329,7 +7395,7 @@
         <v>26</v>
       </c>
       <c r="AA17" s="19" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
@@ -7428,10 +7494,10 @@
         <v>16</v>
       </c>
       <c r="Z18" s="10" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="AA18" s="11" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
@@ -7561,7 +7627,7 @@
         <v>16</v>
       </c>
       <c r="Z20" s="10" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="AA20" s="11" t="s">
         <v>23</v>
@@ -7694,10 +7760,10 @@
         <v>16</v>
       </c>
       <c r="Z22" s="10" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="AA22" s="11" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.25">
@@ -7827,7 +7893,7 @@
         <v>16</v>
       </c>
       <c r="Z24" s="10" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="AA24" s="11" t="s">
         <v>23</v>
@@ -7960,10 +8026,10 @@
         <v>16</v>
       </c>
       <c r="Z26" s="10" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="AA26" s="11" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.25">
@@ -8196,7 +8262,7 @@
         <v>17</v>
       </c>
       <c r="AA29" s="19" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.25">
@@ -8389,7 +8455,7 @@
         <v>14</v>
       </c>
       <c r="X31" s="18" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="Y31" s="18" t="s">
         <v>66</v>
@@ -8398,7 +8464,7 @@
         <v>26</v>
       </c>
       <c r="AA31" s="19" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.25">
@@ -8733,7 +8799,7 @@
         <v>17</v>
       </c>
       <c r="AA35" s="19" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.25">
@@ -8832,7 +8898,7 @@
         <v>16</v>
       </c>
       <c r="Z36" s="10" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="AA36" s="11" t="s">
         <v>23</v>
@@ -8965,7 +9031,7 @@
         <v>16</v>
       </c>
       <c r="Z38" s="10" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="AA38" s="11" t="s">
         <v>23</v>
@@ -9098,7 +9164,7 @@
         <v>16</v>
       </c>
       <c r="Z40" s="10" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="AA40" s="11" t="s">
         <v>23</v>
@@ -9231,7 +9297,7 @@
         <v>16</v>
       </c>
       <c r="Z42" s="10" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="AA42" s="11" t="s">
         <v>23</v>
@@ -9364,7 +9430,7 @@
         <v>16</v>
       </c>
       <c r="Z44" s="10" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="AA44" s="11" t="s">
         <v>23</v>
@@ -9497,7 +9563,7 @@
         <v>16</v>
       </c>
       <c r="Z46" s="10" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="AA46" s="11" t="s">
         <v>23</v>
@@ -9536,7 +9602,7 @@
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="20" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B50" s="20" t="s">
         <v>74</v>
@@ -9577,13 +9643,13 @@
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="23" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="B51" s="21">
         <v>0</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="D51" s="21">
         <v>1</v>
@@ -9622,7 +9688,7 @@
         <v>1</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="D52" s="21">
         <v>0</v>
@@ -9657,7 +9723,7 @@
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="23" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="B53" s="21">
         <v>2</v>
@@ -9671,11 +9737,15 @@
       <c r="E53" s="21">
         <v>1</v>
       </c>
-      <c r="F53" s="21"/>
+      <c r="F53" s="21" t="s">
+        <v>92</v>
+      </c>
       <c r="G53" s="21"/>
       <c r="H53" s="21"/>
       <c r="I53" s="21"/>
-      <c r="J53" s="21"/>
+      <c r="J53" s="21" t="s">
+        <v>93</v>
+      </c>
       <c r="K53" s="21"/>
       <c r="L53" s="21"/>
       <c r="M53" s="21"/>
@@ -9701,7 +9771,7 @@
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="23" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="B55" s="21">
         <v>4</v>
@@ -9715,11 +9785,15 @@
       <c r="E55" s="21">
         <v>1</v>
       </c>
-      <c r="F55" s="21"/>
+      <c r="F55" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="G55" s="21"/>
       <c r="H55" s="21"/>
       <c r="I55" s="21"/>
-      <c r="J55" s="21"/>
+      <c r="J55" s="21" t="s">
+        <v>95</v>
+      </c>
       <c r="K55" s="21"/>
       <c r="L55" s="21"/>
       <c r="M55" s="21"/>
@@ -9745,7 +9819,7 @@
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="23" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B57" s="21">
         <v>6</v>
@@ -9759,11 +9833,15 @@
       <c r="E57" s="21">
         <v>1</v>
       </c>
-      <c r="F57" s="21"/>
+      <c r="F57" s="21" t="s">
+        <v>96</v>
+      </c>
       <c r="G57" s="21"/>
       <c r="H57" s="21"/>
       <c r="I57" s="21"/>
-      <c r="J57" s="21"/>
+      <c r="J57" s="21" t="s">
+        <v>97</v>
+      </c>
       <c r="K57" s="21"/>
       <c r="L57" s="21"/>
       <c r="M57" s="21"/>
@@ -9789,7 +9867,7 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="23" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B59" s="21">
         <v>8</v>
@@ -9803,11 +9881,15 @@
       <c r="E59" s="21">
         <v>1</v>
       </c>
-      <c r="F59" s="21"/>
+      <c r="F59" s="21" t="s">
+        <v>98</v>
+      </c>
       <c r="G59" s="21"/>
       <c r="H59" s="21"/>
       <c r="I59" s="21"/>
-      <c r="J59" s="21"/>
+      <c r="J59" s="21" t="s">
+        <v>99</v>
+      </c>
       <c r="K59" s="21"/>
       <c r="L59" s="21"/>
       <c r="M59" s="21"/>
@@ -9833,10 +9915,10 @@
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="23" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="B61" s="21" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="C61" s="21" t="s">
         <v>91</v>
@@ -9847,11 +9929,15 @@
       <c r="E61" s="21">
         <v>1</v>
       </c>
-      <c r="F61" s="21"/>
+      <c r="F61" s="21" t="s">
+        <v>100</v>
+      </c>
       <c r="G61" s="21"/>
       <c r="H61" s="21"/>
       <c r="I61" s="21"/>
-      <c r="J61" s="21"/>
+      <c r="J61" s="21" t="s">
+        <v>101</v>
+      </c>
       <c r="K61" s="21"/>
       <c r="L61" s="21"/>
       <c r="M61" s="21"/>
@@ -9859,7 +9945,7 @@
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="23"/>
       <c r="B62" s="21" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="C62" s="21"/>
       <c r="D62" s="21"/>
@@ -9877,10 +9963,10 @@
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="23" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="B63" s="21" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="C63" s="21" t="s">
         <v>91</v>
@@ -9891,11 +9977,15 @@
       <c r="E63" s="21">
         <v>1</v>
       </c>
-      <c r="F63" s="21"/>
+      <c r="F63" s="21" t="s">
+        <v>102</v>
+      </c>
       <c r="G63" s="21"/>
       <c r="H63" s="21"/>
       <c r="I63" s="21"/>
-      <c r="J63" s="21"/>
+      <c r="J63" s="21" t="s">
+        <v>103</v>
+      </c>
       <c r="K63" s="21"/>
       <c r="L63" s="21"/>
       <c r="M63" s="21"/>
@@ -9921,10 +10011,10 @@
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="23" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="B65" s="21" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="C65" s="21"/>
       <c r="D65" s="21"/>
@@ -9943,7 +10033,7 @@
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="23"/>
       <c r="B66" s="21" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="C66" s="21"/>
       <c r="D66" s="21"/>
@@ -9961,21 +10051,21 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="20" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="B69" s="20" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="C69" s="20" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="22" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B70" s="22" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C70" s="22">
         <v>4104</v>
@@ -9983,10 +10073,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="22" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B71" s="22" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C71" s="22">
         <v>8200</v>
@@ -9994,10 +10084,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="22" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="B72" s="22" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="C72" s="22">
         <v>8328</v>
@@ -10005,7 +10095,7 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="22" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B73" s="22" t="s">
         <v>13</v>
@@ -10016,10 +10106,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="22" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B74" s="22" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C74" s="22">
         <v>34</v>
@@ -10027,10 +10117,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="B75" s="22" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="C75" s="22">
         <v>512</v>
@@ -10038,10 +10128,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="B76" s="22" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C76" s="22">
         <v>546</v>
@@ -10176,7 +10266,7 @@
         <v>3</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>5</v>
@@ -10562,7 +10652,7 @@
         <v>51</v>
       </c>
       <c r="AA6" s="11" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
@@ -10825,10 +10915,10 @@
         <v>16</v>
       </c>
       <c r="Z10" s="10" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="AA10" s="11" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
@@ -10928,7 +11018,7 @@
         <v>26</v>
       </c>
       <c r="AA11" s="19" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
@@ -11027,7 +11117,7 @@
         <v>16</v>
       </c>
       <c r="Z12" s="10" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="AA12" s="11" t="s">
         <v>23</v>
@@ -11130,7 +11220,7 @@
         <v>32</v>
       </c>
       <c r="AA13" s="19" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
@@ -11229,10 +11319,10 @@
         <v>16</v>
       </c>
       <c r="Z14" s="10" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="AA14" s="11" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
@@ -11362,7 +11452,7 @@
         <v>16</v>
       </c>
       <c r="Z16" s="10" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="AA16" s="11" t="s">
         <v>23</v>
@@ -11465,7 +11555,7 @@
         <v>43</v>
       </c>
       <c r="AA17" s="19" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
@@ -11567,7 +11657,7 @@
         <v>17</v>
       </c>
       <c r="AA18" s="11" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
@@ -12096,10 +12186,10 @@
         <v>16</v>
       </c>
       <c r="Z26" s="10" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="AA26" s="11" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.25">
@@ -12229,7 +12319,7 @@
         <v>16</v>
       </c>
       <c r="Z28" s="10" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="AA28" s="11" t="s">
         <v>23</v>
@@ -12332,7 +12422,7 @@
         <v>26</v>
       </c>
       <c r="AA29" s="19" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.25">
@@ -12431,7 +12521,7 @@
         <v>16</v>
       </c>
       <c r="Z30" s="10" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="AA30" s="11" t="s">
         <v>23</v>
@@ -12534,7 +12624,7 @@
         <v>32</v>
       </c>
       <c r="AA31" s="19" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.25">
@@ -12633,7 +12723,7 @@
         <v>16</v>
       </c>
       <c r="Z32" s="10" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="AA32" s="11" t="s">
         <v>23</v>
@@ -12766,7 +12856,7 @@
         <v>16</v>
       </c>
       <c r="Z34" s="10" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="AA34" s="11" t="s">
         <v>23</v>
@@ -12869,7 +12959,7 @@
         <v>43</v>
       </c>
       <c r="AA35" s="19" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.25">
@@ -13500,7 +13590,7 @@
         <v>16</v>
       </c>
       <c r="Z44" s="10" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="AA44" s="11" t="s">
         <v>23</v>
@@ -13633,7 +13723,7 @@
         <v>16</v>
       </c>
       <c r="Z46" s="10" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="AA46" s="11" t="s">
         <v>23</v>
@@ -13672,7 +13762,7 @@
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="20" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B50" s="20" t="s">
         <v>74</v>
@@ -13713,13 +13803,13 @@
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="23" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="B51" s="21">
         <v>0</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="D51" s="21">
         <v>0</v>
@@ -13727,11 +13817,15 @@
       <c r="E51" s="21">
         <v>1</v>
       </c>
-      <c r="F51" s="21"/>
+      <c r="F51" s="21" t="s">
+        <v>98</v>
+      </c>
       <c r="G51" s="21"/>
       <c r="H51" s="21"/>
       <c r="I51" s="21"/>
-      <c r="J51" s="21"/>
+      <c r="J51" s="21" t="s">
+        <v>99</v>
+      </c>
       <c r="K51" s="21"/>
       <c r="L51" s="21"/>
       <c r="M51" s="21"/>
@@ -13742,7 +13836,7 @@
         <v>1</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="D52" s="21">
         <v>0</v>
@@ -13781,7 +13875,7 @@
         <v>2</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D53" s="21">
         <v>0</v>
@@ -13820,7 +13914,7 @@
         <v>3</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="D54" s="21">
         <v>1</v>
@@ -13855,7 +13949,7 @@
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="23" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="B55" s="21">
         <v>4</v>
@@ -13869,11 +13963,15 @@
       <c r="E55" s="21">
         <v>1</v>
       </c>
-      <c r="F55" s="21"/>
+      <c r="F55" s="21" t="s">
+        <v>92</v>
+      </c>
       <c r="G55" s="21"/>
       <c r="H55" s="21"/>
       <c r="I55" s="21"/>
-      <c r="J55" s="21"/>
+      <c r="J55" s="21" t="s">
+        <v>93</v>
+      </c>
       <c r="K55" s="21"/>
       <c r="L55" s="21"/>
       <c r="M55" s="21"/>
@@ -13884,7 +13982,7 @@
         <v>5</v>
       </c>
       <c r="C56" s="21" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="D56" s="21">
         <v>0</v>
@@ -13892,11 +13990,15 @@
       <c r="E56" s="21">
         <v>1</v>
       </c>
-      <c r="F56" s="21"/>
+      <c r="F56" s="21" t="s">
+        <v>100</v>
+      </c>
       <c r="G56" s="21"/>
       <c r="H56" s="21"/>
       <c r="I56" s="21"/>
-      <c r="J56" s="21"/>
+      <c r="J56" s="21" t="s">
+        <v>101</v>
+      </c>
       <c r="K56" s="21"/>
       <c r="L56" s="21"/>
       <c r="M56" s="21"/>
@@ -13941,7 +14043,7 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="23" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="B59" s="21">
         <v>8</v>
@@ -13955,11 +14057,15 @@
       <c r="E59" s="21">
         <v>1</v>
       </c>
-      <c r="F59" s="21"/>
+      <c r="F59" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="G59" s="21"/>
       <c r="H59" s="21"/>
       <c r="I59" s="21"/>
-      <c r="J59" s="21"/>
+      <c r="J59" s="21" t="s">
+        <v>95</v>
+      </c>
       <c r="K59" s="21"/>
       <c r="L59" s="21"/>
       <c r="M59" s="21"/>
@@ -13970,7 +14076,7 @@
         <v>9</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="D60" s="21">
         <v>0</v>
@@ -13978,11 +14084,15 @@
       <c r="E60" s="21">
         <v>1</v>
       </c>
-      <c r="F60" s="21"/>
+      <c r="F60" s="21" t="s">
+        <v>102</v>
+      </c>
       <c r="G60" s="21"/>
       <c r="H60" s="21"/>
       <c r="I60" s="21"/>
-      <c r="J60" s="21"/>
+      <c r="J60" s="21" t="s">
+        <v>103</v>
+      </c>
       <c r="K60" s="21"/>
       <c r="L60" s="21"/>
       <c r="M60" s="21"/>
@@ -13990,7 +14100,7 @@
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="23"/>
       <c r="B61" s="21" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="C61" s="21"/>
       <c r="D61" s="21"/>
@@ -14009,7 +14119,7 @@
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="23"/>
       <c r="B62" s="21" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="C62" s="21"/>
       <c r="D62" s="21"/>
@@ -14027,10 +14137,10 @@
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="23" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B63" s="21" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="C63" s="21" t="s">
         <v>91</v>
@@ -14041,11 +14151,15 @@
       <c r="E63" s="21">
         <v>1</v>
       </c>
-      <c r="F63" s="21"/>
+      <c r="F63" s="21" t="s">
+        <v>96</v>
+      </c>
       <c r="G63" s="21"/>
       <c r="H63" s="21"/>
       <c r="I63" s="21"/>
-      <c r="J63" s="21"/>
+      <c r="J63" s="21" t="s">
+        <v>97</v>
+      </c>
       <c r="K63" s="21"/>
       <c r="L63" s="21"/>
       <c r="M63" s="21"/>
@@ -14072,7 +14186,7 @@
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="23"/>
       <c r="B65" s="21" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="C65" s="21"/>
       <c r="D65" s="21"/>
@@ -14091,7 +14205,7 @@
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="23"/>
       <c r="B66" s="21" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="C66" s="21"/>
       <c r="D66" s="21"/>
@@ -14109,21 +14223,21 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="20" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="B69" s="20" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="C69" s="20" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="22" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B70" s="22" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C70" s="22">
         <v>4104</v>
@@ -14131,10 +14245,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="22" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B71" s="22" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C71" s="22">
         <v>8200</v>
@@ -14142,10 +14256,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="22" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="B72" s="22" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="C72" s="22">
         <v>8328</v>
@@ -14153,7 +14267,7 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="22" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B73" s="22" t="s">
         <v>13</v>
@@ -14164,10 +14278,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="22" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B74" s="22" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C74" s="22">
         <v>34</v>
@@ -14175,10 +14289,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="B75" s="22" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="C75" s="22">
         <v>512</v>
@@ -14186,10 +14300,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="B76" s="22" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C76" s="22">
         <v>546</v>
@@ -15041,7 +15155,7 @@
         <v>43</v>
       </c>
       <c r="Z11" s="19" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
@@ -15235,7 +15349,7 @@
         <v>51</v>
       </c>
       <c r="Z13" s="19" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
@@ -15333,7 +15447,7 @@
         <v>57</v>
       </c>
       <c r="Z14" s="11" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
@@ -15557,7 +15671,7 @@
         <v>63</v>
       </c>
       <c r="Z17" s="19" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
@@ -15652,10 +15766,10 @@
         <v>16</v>
       </c>
       <c r="Y18" s="10" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="Z18" s="11" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
@@ -15780,7 +15894,7 @@
         <v>16</v>
       </c>
       <c r="Y20" s="10" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="Z20" s="11" t="s">
         <v>23</v>
@@ -15908,10 +16022,10 @@
         <v>16</v>
       </c>
       <c r="Y22" s="10" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="Z22" s="11" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
@@ -16036,7 +16150,7 @@
         <v>16</v>
       </c>
       <c r="Y24" s="10" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="Z24" s="11" t="s">
         <v>23</v>
@@ -16164,10 +16278,10 @@
         <v>16</v>
       </c>
       <c r="Y26" s="10" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="Z26" s="11" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.25">
@@ -16391,7 +16505,7 @@
         <v>43</v>
       </c>
       <c r="Z29" s="19" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.25">
@@ -16585,7 +16699,7 @@
         <v>51</v>
       </c>
       <c r="Z31" s="19" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.25">
@@ -16907,7 +17021,7 @@
         <v>63</v>
       </c>
       <c r="Z35" s="19" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.25">
@@ -17002,7 +17116,7 @@
         <v>16</v>
       </c>
       <c r="Y36" s="10" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="Z36" s="11" t="s">
         <v>23</v>
@@ -17130,7 +17244,7 @@
         <v>16</v>
       </c>
       <c r="Y38" s="10" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="Z38" s="11" t="s">
         <v>23</v>
@@ -17258,7 +17372,7 @@
         <v>16</v>
       </c>
       <c r="Y40" s="10" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="Z40" s="11" t="s">
         <v>23</v>
@@ -17386,7 +17500,7 @@
         <v>16</v>
       </c>
       <c r="Y42" s="10" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="Z42" s="11" t="s">
         <v>23</v>
@@ -17514,7 +17628,7 @@
         <v>16</v>
       </c>
       <c r="Y44" s="10" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="Z44" s="11" t="s">
         <v>23</v>
@@ -17642,7 +17756,7 @@
         <v>16</v>
       </c>
       <c r="Y46" s="10" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="Z46" s="11" t="s">
         <v>23</v>
@@ -17729,11 +17843,15 @@
       <c r="D51" s="21">
         <v>1</v>
       </c>
-      <c r="E51" s="21"/>
+      <c r="E51" s="21" t="s">
+        <v>174</v>
+      </c>
       <c r="F51" s="21"/>
       <c r="G51" s="21"/>
       <c r="H51" s="21"/>
-      <c r="I51" s="21"/>
+      <c r="I51" s="21" t="s">
+        <v>175</v>
+      </c>
       <c r="J51" s="21"/>
       <c r="K51" s="21"/>
       <c r="L51" s="21"/>
@@ -17743,7 +17861,7 @@
         <v>1</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="C52" s="21">
         <v>0</v>
@@ -17751,11 +17869,15 @@
       <c r="D52" s="21">
         <v>1</v>
       </c>
-      <c r="E52" s="21"/>
+      <c r="E52" s="21" t="s">
+        <v>92</v>
+      </c>
       <c r="F52" s="21"/>
       <c r="G52" s="21"/>
       <c r="H52" s="21"/>
-      <c r="I52" s="21"/>
+      <c r="I52" s="21" t="s">
+        <v>93</v>
+      </c>
       <c r="J52" s="21"/>
       <c r="K52" s="21"/>
       <c r="L52" s="21"/>
@@ -17765,7 +17887,7 @@
         <v>2</v>
       </c>
       <c r="B53" s="21" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="C53" s="21">
         <v>0</v>
@@ -17773,11 +17895,15 @@
       <c r="D53" s="21">
         <v>1</v>
       </c>
-      <c r="E53" s="21"/>
+      <c r="E53" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="F53" s="21"/>
       <c r="G53" s="21"/>
       <c r="H53" s="21"/>
-      <c r="I53" s="21"/>
+      <c r="I53" s="21" t="s">
+        <v>95</v>
+      </c>
       <c r="J53" s="21"/>
       <c r="K53" s="21"/>
       <c r="L53" s="21"/>
@@ -17787,7 +17913,7 @@
         <v>3</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="C54" s="21">
         <v>0</v>
@@ -17825,7 +17951,7 @@
         <v>4</v>
       </c>
       <c r="B55" s="21" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="C55" s="21">
         <v>0</v>
@@ -17863,7 +17989,7 @@
         <v>5</v>
       </c>
       <c r="B56" s="21" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="C56" s="21">
         <v>0</v>
@@ -17871,11 +17997,15 @@
       <c r="D56" s="21">
         <v>1</v>
       </c>
-      <c r="E56" s="21"/>
+      <c r="E56" s="21" t="s">
+        <v>96</v>
+      </c>
       <c r="F56" s="21"/>
       <c r="G56" s="21"/>
       <c r="H56" s="21"/>
-      <c r="I56" s="21"/>
+      <c r="I56" s="21" t="s">
+        <v>97</v>
+      </c>
       <c r="J56" s="21"/>
       <c r="K56" s="21"/>
       <c r="L56" s="21"/>
@@ -17885,7 +18015,7 @@
         <v>6</v>
       </c>
       <c r="B57" s="21" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="C57" s="21">
         <v>1</v>
@@ -17931,11 +18061,15 @@
       <c r="D58" s="21">
         <v>1</v>
       </c>
-      <c r="E58" s="21"/>
+      <c r="E58" s="21" t="s">
+        <v>98</v>
+      </c>
       <c r="F58" s="21"/>
       <c r="G58" s="21"/>
       <c r="H58" s="21"/>
-      <c r="I58" s="21"/>
+      <c r="I58" s="21" t="s">
+        <v>99</v>
+      </c>
       <c r="J58" s="21"/>
       <c r="K58" s="21"/>
       <c r="L58" s="21"/>
@@ -17945,7 +18079,7 @@
         <v>8</v>
       </c>
       <c r="B59" s="21" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="C59" s="21">
         <v>0</v>
@@ -17953,11 +18087,15 @@
       <c r="D59" s="21">
         <v>1</v>
       </c>
-      <c r="E59" s="21"/>
+      <c r="E59" s="21" t="s">
+        <v>100</v>
+      </c>
       <c r="F59" s="21"/>
       <c r="G59" s="21"/>
       <c r="H59" s="21"/>
-      <c r="I59" s="21"/>
+      <c r="I59" s="21" t="s">
+        <v>101</v>
+      </c>
       <c r="J59" s="21"/>
       <c r="K59" s="21"/>
       <c r="L59" s="21"/>
@@ -17967,7 +18105,7 @@
         <v>9</v>
       </c>
       <c r="B60" s="21" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="C60" s="21">
         <v>0</v>
@@ -17975,18 +18113,22 @@
       <c r="D60" s="21">
         <v>1</v>
       </c>
-      <c r="E60" s="21"/>
+      <c r="E60" s="21" t="s">
+        <v>102</v>
+      </c>
       <c r="F60" s="21"/>
       <c r="G60" s="21"/>
       <c r="H60" s="21"/>
-      <c r="I60" s="21"/>
+      <c r="I60" s="21" t="s">
+        <v>103</v>
+      </c>
       <c r="J60" s="21"/>
       <c r="K60" s="21"/>
       <c r="L60" s="21"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="21" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="B61" s="21"/>
       <c r="C61" s="21"/>
@@ -18004,7 +18146,7 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="21" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B62" s="21"/>
       <c r="C62" s="21"/>
@@ -18022,7 +18164,7 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="21" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B63" s="21"/>
       <c r="C63" s="21"/>
@@ -18058,7 +18200,7 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="21" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="B65" s="21"/>
       <c r="C65" s="21"/>
@@ -18076,7 +18218,7 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="21" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="B66" s="21"/>
       <c r="C66" s="21"/>
@@ -18094,21 +18236,21 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="20" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="B69" s="20" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="C69" s="20" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="22" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B70" s="22" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C70" s="22">
         <v>4104</v>
@@ -18116,10 +18258,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="22" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B71" s="22" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C71" s="22">
         <v>8200</v>
@@ -18127,10 +18269,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="22" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="B72" s="22" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="C72" s="22">
         <v>8328</v>
@@ -18138,7 +18280,7 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="22" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B73" s="22" t="s">
         <v>13</v>
@@ -18149,10 +18291,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="22" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B74" s="22" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C74" s="22">
         <v>34</v>
@@ -18160,10 +18302,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="B75" s="22" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="C75" s="22">
         <v>512</v>
@@ -18171,10 +18313,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="B76" s="22" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C76" s="22">
         <v>546</v>
@@ -18241,22 +18383,22 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="E1" s="24" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="G1" s="24" t="s">
         <v>3</v>
@@ -18320,11 +18462,15 @@
       <c r="I2" s="22">
         <v>1</v>
       </c>
-      <c r="J2" s="21"/>
+      <c r="J2" s="21" t="s">
+        <v>174</v>
+      </c>
       <c r="K2" s="21"/>
       <c r="L2" s="21"/>
       <c r="M2" s="21"/>
-      <c r="N2" s="21"/>
+      <c r="N2" s="21" t="s">
+        <v>175</v>
+      </c>
       <c r="O2" s="21"/>
       <c r="P2" s="21"/>
       <c r="Q2" s="21"/>
@@ -18357,11 +18503,15 @@
       <c r="I3" s="22">
         <v>1</v>
       </c>
-      <c r="J3" s="21"/>
+      <c r="J3" s="21" t="s">
+        <v>174</v>
+      </c>
       <c r="K3" s="21"/>
       <c r="L3" s="21"/>
       <c r="M3" s="21"/>
-      <c r="N3" s="21"/>
+      <c r="N3" s="21" t="s">
+        <v>175</v>
+      </c>
       <c r="O3" s="21"/>
       <c r="P3" s="21"/>
       <c r="Q3" s="21"/>
@@ -18394,11 +18544,15 @@
       <c r="I4" s="22">
         <v>1</v>
       </c>
-      <c r="J4" s="21"/>
+      <c r="J4" s="21" t="s">
+        <v>92</v>
+      </c>
       <c r="K4" s="21"/>
       <c r="L4" s="21"/>
       <c r="M4" s="21"/>
-      <c r="N4" s="21"/>
+      <c r="N4" s="21" t="s">
+        <v>93</v>
+      </c>
       <c r="O4" s="21"/>
       <c r="P4" s="21"/>
       <c r="Q4" s="21"/>
@@ -18431,11 +18585,15 @@
       <c r="I5" s="22">
         <v>1</v>
       </c>
-      <c r="J5" s="21"/>
+      <c r="J5" s="21" t="s">
+        <v>92</v>
+      </c>
       <c r="K5" s="21"/>
       <c r="L5" s="21"/>
       <c r="M5" s="21"/>
-      <c r="N5" s="21"/>
+      <c r="N5" s="21" t="s">
+        <v>93</v>
+      </c>
       <c r="O5" s="21"/>
       <c r="P5" s="21"/>
       <c r="Q5" s="21"/>
@@ -18468,11 +18626,15 @@
       <c r="I6" s="22">
         <v>1</v>
       </c>
-      <c r="J6" s="21"/>
+      <c r="J6" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="K6" s="21"/>
       <c r="L6" s="21"/>
       <c r="M6" s="21"/>
-      <c r="N6" s="21"/>
+      <c r="N6" s="21" t="s">
+        <v>95</v>
+      </c>
       <c r="O6" s="21"/>
       <c r="P6" s="21"/>
       <c r="Q6" s="21"/>
@@ -18491,13 +18653,13 @@
         <v>34</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="F7" s="22" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="H7" s="22">
         <v>0</v>
@@ -18558,11 +18720,15 @@
       <c r="I8" s="22">
         <v>1</v>
       </c>
-      <c r="J8" s="21"/>
+      <c r="J8" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="K8" s="21"/>
       <c r="L8" s="21"/>
       <c r="M8" s="21"/>
-      <c r="N8" s="21"/>
+      <c r="N8" s="21" t="s">
+        <v>95</v>
+      </c>
       <c r="O8" s="21"/>
       <c r="P8" s="21"/>
       <c r="Q8" s="21"/>
@@ -18581,13 +18747,13 @@
         <v>39</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="F9" s="22" t="s">
         <v>17</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="H9" s="22">
         <v>0</v>
@@ -18648,11 +18814,15 @@
       <c r="I10" s="22">
         <v>1</v>
       </c>
-      <c r="J10" s="21"/>
+      <c r="J10" s="21" t="s">
+        <v>96</v>
+      </c>
       <c r="K10" s="21"/>
       <c r="L10" s="21"/>
       <c r="M10" s="21"/>
-      <c r="N10" s="21"/>
+      <c r="N10" s="21" t="s">
+        <v>97</v>
+      </c>
       <c r="O10" s="21"/>
       <c r="P10" s="21"/>
       <c r="Q10" s="21"/>
@@ -18685,11 +18855,15 @@
       <c r="I11" s="22">
         <v>1</v>
       </c>
-      <c r="J11" s="21"/>
+      <c r="J11" s="21" t="s">
+        <v>96</v>
+      </c>
       <c r="K11" s="21"/>
       <c r="L11" s="21"/>
       <c r="M11" s="21"/>
-      <c r="N11" s="21"/>
+      <c r="N11" s="21" t="s">
+        <v>97</v>
+      </c>
       <c r="O11" s="21"/>
       <c r="P11" s="21"/>
       <c r="Q11" s="21"/>
@@ -18708,7 +18882,7 @@
         <v>47</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="F12" s="22" t="s">
         <v>17</v>
@@ -18775,11 +18949,15 @@
       <c r="I13" s="22">
         <v>1</v>
       </c>
-      <c r="J13" s="21"/>
+      <c r="J13" s="21" t="s">
+        <v>98</v>
+      </c>
       <c r="K13" s="21"/>
       <c r="L13" s="21"/>
       <c r="M13" s="21"/>
-      <c r="N13" s="21"/>
+      <c r="N13" s="21" t="s">
+        <v>99</v>
+      </c>
       <c r="O13" s="21"/>
       <c r="P13" s="21"/>
       <c r="Q13" s="21"/>
@@ -18812,11 +18990,15 @@
       <c r="I14" s="22">
         <v>1</v>
       </c>
-      <c r="J14" s="21"/>
+      <c r="J14" s="21" t="s">
+        <v>98</v>
+      </c>
       <c r="K14" s="21"/>
       <c r="L14" s="21"/>
       <c r="M14" s="21"/>
-      <c r="N14" s="21"/>
+      <c r="N14" s="21" t="s">
+        <v>99</v>
+      </c>
       <c r="O14" s="21"/>
       <c r="P14" s="21"/>
       <c r="Q14" s="21"/>
@@ -18849,11 +19031,15 @@
       <c r="I15" s="22">
         <v>1</v>
       </c>
-      <c r="J15" s="21"/>
+      <c r="J15" s="21" t="s">
+        <v>100</v>
+      </c>
       <c r="K15" s="21"/>
       <c r="L15" s="21"/>
       <c r="M15" s="21"/>
-      <c r="N15" s="21"/>
+      <c r="N15" s="21" t="s">
+        <v>101</v>
+      </c>
       <c r="O15" s="21"/>
       <c r="P15" s="21"/>
       <c r="Q15" s="21"/>
@@ -18886,11 +19072,15 @@
       <c r="I16" s="22">
         <v>1</v>
       </c>
-      <c r="J16" s="21"/>
+      <c r="J16" s="21" t="s">
+        <v>100</v>
+      </c>
       <c r="K16" s="21"/>
       <c r="L16" s="21"/>
       <c r="M16" s="21"/>
-      <c r="N16" s="21"/>
+      <c r="N16" s="21" t="s">
+        <v>101</v>
+      </c>
       <c r="O16" s="21"/>
       <c r="P16" s="21"/>
       <c r="Q16" s="21"/>
@@ -18923,11 +19113,15 @@
       <c r="I17" s="22">
         <v>1</v>
       </c>
-      <c r="J17" s="21"/>
+      <c r="J17" s="21" t="s">
+        <v>102</v>
+      </c>
       <c r="K17" s="21"/>
       <c r="L17" s="21"/>
       <c r="M17" s="21"/>
-      <c r="N17" s="21"/>
+      <c r="N17" s="21" t="s">
+        <v>103</v>
+      </c>
       <c r="O17" s="21"/>
       <c r="P17" s="21"/>
       <c r="Q17" s="21"/>
@@ -18960,11 +19154,15 @@
       <c r="I18" s="22">
         <v>1</v>
       </c>
-      <c r="J18" s="21"/>
+      <c r="J18" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="K18" s="21"/>
       <c r="L18" s="21"/>
       <c r="M18" s="21"/>
-      <c r="N18" s="21"/>
+      <c r="N18" s="21" t="s">
+        <v>95</v>
+      </c>
       <c r="O18" s="21"/>
       <c r="P18" s="21"/>
       <c r="Q18" s="21"/>
@@ -18983,13 +19181,13 @@
         <v>65</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="F19" s="22" t="s">
         <v>17</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="H19" s="22">
         <v>0</v>
@@ -19050,11 +19248,15 @@
       <c r="I20" s="22">
         <v>1</v>
       </c>
-      <c r="J20" s="21"/>
+      <c r="J20" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="K20" s="21"/>
       <c r="L20" s="21"/>
       <c r="M20" s="21"/>
-      <c r="N20" s="21"/>
+      <c r="N20" s="21" t="s">
+        <v>95</v>
+      </c>
       <c r="O20" s="21"/>
       <c r="P20" s="21"/>
       <c r="Q20" s="21"/>
@@ -19073,13 +19275,13 @@
         <v>68</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="F21" s="22" t="s">
         <v>17</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="H21" s="22">
         <v>0</v>
@@ -19140,11 +19342,15 @@
       <c r="I22" s="22">
         <v>1</v>
       </c>
-      <c r="J22" s="21"/>
+      <c r="J22" s="21" t="s">
+        <v>96</v>
+      </c>
       <c r="K22" s="21"/>
       <c r="L22" s="21"/>
       <c r="M22" s="21"/>
-      <c r="N22" s="21"/>
+      <c r="N22" s="21" t="s">
+        <v>97</v>
+      </c>
       <c r="O22" s="21"/>
       <c r="P22" s="21"/>
       <c r="Q22" s="21"/>
@@ -19177,11 +19383,15 @@
       <c r="I23" s="22">
         <v>1</v>
       </c>
-      <c r="J23" s="21"/>
+      <c r="J23" s="21" t="s">
+        <v>96</v>
+      </c>
       <c r="K23" s="21"/>
       <c r="L23" s="21"/>
       <c r="M23" s="21"/>
-      <c r="N23" s="21"/>
+      <c r="N23" s="21" t="s">
+        <v>97</v>
+      </c>
       <c r="O23" s="21"/>
       <c r="P23" s="21"/>
       <c r="Q23" s="21"/>
@@ -19200,7 +19410,7 @@
         <v>70</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="F24" s="22" t="s">
         <v>17</v>
@@ -19267,11 +19477,15 @@
       <c r="I25" s="22">
         <v>1</v>
       </c>
-      <c r="J25" s="21"/>
+      <c r="J25" s="21" t="s">
+        <v>98</v>
+      </c>
       <c r="K25" s="21"/>
       <c r="L25" s="21"/>
       <c r="M25" s="21"/>
-      <c r="N25" s="21"/>
+      <c r="N25" s="21" t="s">
+        <v>99</v>
+      </c>
       <c r="O25" s="21"/>
       <c r="P25" s="21"/>
       <c r="Q25" s="21"/>
@@ -19304,11 +19518,15 @@
       <c r="I26" s="22">
         <v>1</v>
       </c>
-      <c r="J26" s="21"/>
+      <c r="J26" s="21" t="s">
+        <v>98</v>
+      </c>
       <c r="K26" s="21"/>
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
-      <c r="N26" s="21"/>
+      <c r="N26" s="21" t="s">
+        <v>99</v>
+      </c>
       <c r="O26" s="21"/>
       <c r="P26" s="21"/>
       <c r="Q26" s="21"/>
@@ -19341,11 +19559,15 @@
       <c r="I27" s="22">
         <v>1</v>
       </c>
-      <c r="J27" s="21"/>
+      <c r="J27" s="21" t="s">
+        <v>100</v>
+      </c>
       <c r="K27" s="21"/>
       <c r="L27" s="21"/>
       <c r="M27" s="21"/>
-      <c r="N27" s="21"/>
+      <c r="N27" s="21" t="s">
+        <v>101</v>
+      </c>
       <c r="O27" s="21"/>
       <c r="P27" s="21"/>
       <c r="Q27" s="21"/>
@@ -19378,11 +19600,15 @@
       <c r="I28" s="22">
         <v>1</v>
       </c>
-      <c r="J28" s="21"/>
+      <c r="J28" s="21" t="s">
+        <v>100</v>
+      </c>
       <c r="K28" s="21"/>
       <c r="L28" s="21"/>
       <c r="M28" s="21"/>
-      <c r="N28" s="21"/>
+      <c r="N28" s="21" t="s">
+        <v>101</v>
+      </c>
       <c r="O28" s="21"/>
       <c r="P28" s="21"/>
       <c r="Q28" s="21"/>
@@ -19415,11 +19641,15 @@
       <c r="I29" s="22">
         <v>1</v>
       </c>
-      <c r="J29" s="21"/>
+      <c r="J29" s="21" t="s">
+        <v>102</v>
+      </c>
       <c r="K29" s="21"/>
       <c r="L29" s="21"/>
       <c r="M29" s="21"/>
-      <c r="N29" s="21"/>
+      <c r="N29" s="21" t="s">
+        <v>103</v>
+      </c>
       <c r="O29" s="21"/>
       <c r="P29" s="21"/>
       <c r="Q29" s="21"/>
@@ -19452,11 +19682,15 @@
       <c r="I30" s="22">
         <v>1</v>
       </c>
-      <c r="J30" s="21"/>
+      <c r="J30" s="21" t="s">
+        <v>102</v>
+      </c>
       <c r="K30" s="21"/>
       <c r="L30" s="21"/>
       <c r="M30" s="21"/>
-      <c r="N30" s="21"/>
+      <c r="N30" s="21" t="s">
+        <v>103</v>
+      </c>
       <c r="O30" s="21"/>
       <c r="P30" s="21"/>
       <c r="Q30" s="21"/>
@@ -19531,22 +19765,22 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="E1" s="24" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="G1" s="24" t="s">
         <v>3</v>
@@ -19610,11 +19844,15 @@
       <c r="I2" s="22">
         <v>1</v>
       </c>
-      <c r="J2" s="21"/>
+      <c r="J2" s="21" t="s">
+        <v>174</v>
+      </c>
       <c r="K2" s="21"/>
       <c r="L2" s="21"/>
       <c r="M2" s="21"/>
-      <c r="N2" s="21"/>
+      <c r="N2" s="21" t="s">
+        <v>175</v>
+      </c>
       <c r="O2" s="21"/>
       <c r="P2" s="21"/>
       <c r="Q2" s="21"/>
@@ -19647,11 +19885,15 @@
       <c r="I3" s="22">
         <v>1</v>
       </c>
-      <c r="J3" s="21"/>
+      <c r="J3" s="21" t="s">
+        <v>174</v>
+      </c>
       <c r="K3" s="21"/>
       <c r="L3" s="21"/>
       <c r="M3" s="21"/>
-      <c r="N3" s="21"/>
+      <c r="N3" s="21" t="s">
+        <v>175</v>
+      </c>
       <c r="O3" s="21"/>
       <c r="P3" s="21"/>
       <c r="Q3" s="21"/>
@@ -19684,11 +19926,15 @@
       <c r="I4" s="22">
         <v>1</v>
       </c>
-      <c r="J4" s="21"/>
+      <c r="J4" s="21" t="s">
+        <v>92</v>
+      </c>
       <c r="K4" s="21"/>
       <c r="L4" s="21"/>
       <c r="M4" s="21"/>
-      <c r="N4" s="21"/>
+      <c r="N4" s="21" t="s">
+        <v>93</v>
+      </c>
       <c r="O4" s="21"/>
       <c r="P4" s="21"/>
       <c r="Q4" s="21"/>
@@ -19721,11 +19967,15 @@
       <c r="I5" s="22">
         <v>1</v>
       </c>
-      <c r="J5" s="21"/>
+      <c r="J5" s="21" t="s">
+        <v>92</v>
+      </c>
       <c r="K5" s="21"/>
       <c r="L5" s="21"/>
       <c r="M5" s="21"/>
-      <c r="N5" s="21"/>
+      <c r="N5" s="21" t="s">
+        <v>93</v>
+      </c>
       <c r="O5" s="21"/>
       <c r="P5" s="21"/>
       <c r="Q5" s="21"/>
@@ -19758,11 +20008,15 @@
       <c r="I6" s="22">
         <v>1</v>
       </c>
-      <c r="J6" s="21"/>
+      <c r="J6" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="K6" s="21"/>
       <c r="L6" s="21"/>
       <c r="M6" s="21"/>
-      <c r="N6" s="21"/>
+      <c r="N6" s="21" t="s">
+        <v>95</v>
+      </c>
       <c r="O6" s="21"/>
       <c r="P6" s="21"/>
       <c r="Q6" s="21"/>
@@ -19787,7 +20041,7 @@
         <v>26</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="H7" s="22">
         <v>0</v>
@@ -19848,11 +20102,15 @@
       <c r="I8" s="22">
         <v>1</v>
       </c>
-      <c r="J8" s="21"/>
+      <c r="J8" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="K8" s="21"/>
       <c r="L8" s="21"/>
       <c r="M8" s="21"/>
-      <c r="N8" s="21"/>
+      <c r="N8" s="21" t="s">
+        <v>95</v>
+      </c>
       <c r="O8" s="21"/>
       <c r="P8" s="21"/>
       <c r="Q8" s="21"/>
@@ -19871,13 +20129,13 @@
         <v>39</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="F9" s="22" t="s">
         <v>17</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="H9" s="22">
         <v>0</v>
@@ -19938,11 +20196,15 @@
       <c r="I10" s="22">
         <v>1</v>
       </c>
-      <c r="J10" s="21"/>
+      <c r="J10" s="21" t="s">
+        <v>96</v>
+      </c>
       <c r="K10" s="21"/>
       <c r="L10" s="21"/>
       <c r="M10" s="21"/>
-      <c r="N10" s="21"/>
+      <c r="N10" s="21" t="s">
+        <v>97</v>
+      </c>
       <c r="O10" s="21"/>
       <c r="P10" s="21"/>
       <c r="Q10" s="21"/>
@@ -19975,11 +20237,15 @@
       <c r="I11" s="22">
         <v>1</v>
       </c>
-      <c r="J11" s="21"/>
+      <c r="J11" s="21" t="s">
+        <v>96</v>
+      </c>
       <c r="K11" s="21"/>
       <c r="L11" s="21"/>
       <c r="M11" s="21"/>
-      <c r="N11" s="21"/>
+      <c r="N11" s="21" t="s">
+        <v>97</v>
+      </c>
       <c r="O11" s="21"/>
       <c r="P11" s="21"/>
       <c r="Q11" s="21"/>
@@ -19998,13 +20264,13 @@
         <v>47</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="F12" s="22" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="H12" s="22">
         <v>1</v>
@@ -20054,7 +20320,7 @@
         <v>14</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="G13" s="22" t="s">
         <v>91</v>
@@ -20065,11 +20331,15 @@
       <c r="I13" s="22">
         <v>1</v>
       </c>
-      <c r="J13" s="21"/>
+      <c r="J13" s="21" t="s">
+        <v>98</v>
+      </c>
       <c r="K13" s="21"/>
       <c r="L13" s="21"/>
       <c r="M13" s="21"/>
-      <c r="N13" s="21"/>
+      <c r="N13" s="21" t="s">
+        <v>99</v>
+      </c>
       <c r="O13" s="21"/>
       <c r="P13" s="21"/>
       <c r="Q13" s="21"/>
@@ -20091,7 +20361,7 @@
         <v>22</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="G14" s="22" t="s">
         <v>91</v>
@@ -20102,11 +20372,15 @@
       <c r="I14" s="22">
         <v>1</v>
       </c>
-      <c r="J14" s="21"/>
+      <c r="J14" s="21" t="s">
+        <v>98</v>
+      </c>
       <c r="K14" s="21"/>
       <c r="L14" s="21"/>
       <c r="M14" s="21"/>
-      <c r="N14" s="21"/>
+      <c r="N14" s="21" t="s">
+        <v>99</v>
+      </c>
       <c r="O14" s="21"/>
       <c r="P14" s="21"/>
       <c r="Q14" s="21"/>
@@ -20128,7 +20402,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="G15" s="22" t="s">
         <v>91</v>
@@ -20139,11 +20413,15 @@
       <c r="I15" s="22">
         <v>1</v>
       </c>
-      <c r="J15" s="21"/>
+      <c r="J15" s="21" t="s">
+        <v>100</v>
+      </c>
       <c r="K15" s="21"/>
       <c r="L15" s="21"/>
       <c r="M15" s="21"/>
-      <c r="N15" s="21"/>
+      <c r="N15" s="21" t="s">
+        <v>101</v>
+      </c>
       <c r="O15" s="21"/>
       <c r="P15" s="21"/>
       <c r="Q15" s="21"/>
@@ -20165,7 +20443,7 @@
         <v>22</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="G16" s="22" t="s">
         <v>91</v>
@@ -20176,11 +20454,15 @@
       <c r="I16" s="22">
         <v>1</v>
       </c>
-      <c r="J16" s="21"/>
+      <c r="J16" s="21" t="s">
+        <v>100</v>
+      </c>
       <c r="K16" s="21"/>
       <c r="L16" s="21"/>
       <c r="M16" s="21"/>
-      <c r="N16" s="21"/>
+      <c r="N16" s="21" t="s">
+        <v>101</v>
+      </c>
       <c r="O16" s="21"/>
       <c r="P16" s="21"/>
       <c r="Q16" s="21"/>
@@ -20202,7 +20484,7 @@
         <v>14</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="G17" s="22" t="s">
         <v>91</v>
@@ -20213,11 +20495,15 @@
       <c r="I17" s="22">
         <v>1</v>
       </c>
-      <c r="J17" s="21"/>
+      <c r="J17" s="21" t="s">
+        <v>102</v>
+      </c>
       <c r="K17" s="21"/>
       <c r="L17" s="21"/>
       <c r="M17" s="21"/>
-      <c r="N17" s="21"/>
+      <c r="N17" s="21" t="s">
+        <v>103</v>
+      </c>
       <c r="O17" s="21"/>
       <c r="P17" s="21"/>
       <c r="Q17" s="21"/>
@@ -20250,11 +20536,15 @@
       <c r="I18" s="22">
         <v>1</v>
       </c>
-      <c r="J18" s="21"/>
+      <c r="J18" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="K18" s="21"/>
       <c r="L18" s="21"/>
       <c r="M18" s="21"/>
-      <c r="N18" s="21"/>
+      <c r="N18" s="21" t="s">
+        <v>95</v>
+      </c>
       <c r="O18" s="21"/>
       <c r="P18" s="21"/>
       <c r="Q18" s="21"/>
@@ -20273,13 +20563,13 @@
         <v>65</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="F19" s="22" t="s">
         <v>17</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="H19" s="22">
         <v>0</v>
@@ -20340,11 +20630,15 @@
       <c r="I20" s="22">
         <v>1</v>
       </c>
-      <c r="J20" s="21"/>
+      <c r="J20" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="K20" s="21"/>
       <c r="L20" s="21"/>
       <c r="M20" s="21"/>
-      <c r="N20" s="21"/>
+      <c r="N20" s="21" t="s">
+        <v>95</v>
+      </c>
       <c r="O20" s="21"/>
       <c r="P20" s="21"/>
       <c r="Q20" s="21"/>
@@ -20363,13 +20657,13 @@
         <v>68</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="F21" s="22" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="H21" s="22">
         <v>0</v>
@@ -20430,11 +20724,15 @@
       <c r="I22" s="22">
         <v>1</v>
       </c>
-      <c r="J22" s="21"/>
+      <c r="J22" s="21" t="s">
+        <v>96</v>
+      </c>
       <c r="K22" s="21"/>
       <c r="L22" s="21"/>
       <c r="M22" s="21"/>
-      <c r="N22" s="21"/>
+      <c r="N22" s="21" t="s">
+        <v>97</v>
+      </c>
       <c r="O22" s="21"/>
       <c r="P22" s="21"/>
       <c r="Q22" s="21"/>
@@ -20467,11 +20765,15 @@
       <c r="I23" s="22">
         <v>1</v>
       </c>
-      <c r="J23" s="21"/>
+      <c r="J23" s="21" t="s">
+        <v>96</v>
+      </c>
       <c r="K23" s="21"/>
       <c r="L23" s="21"/>
       <c r="M23" s="21"/>
-      <c r="N23" s="21"/>
+      <c r="N23" s="21" t="s">
+        <v>97</v>
+      </c>
       <c r="O23" s="21"/>
       <c r="P23" s="21"/>
       <c r="Q23" s="21"/>
@@ -20490,13 +20792,13 @@
         <v>70</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="F24" s="22" t="s">
         <v>17</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="H24" s="22">
         <v>1</v>
@@ -20546,7 +20848,7 @@
         <v>22</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="G25" s="22" t="s">
         <v>91</v>
@@ -20557,11 +20859,15 @@
       <c r="I25" s="22">
         <v>1</v>
       </c>
-      <c r="J25" s="21"/>
+      <c r="J25" s="21" t="s">
+        <v>98</v>
+      </c>
       <c r="K25" s="21"/>
       <c r="L25" s="21"/>
       <c r="M25" s="21"/>
-      <c r="N25" s="21"/>
+      <c r="N25" s="21" t="s">
+        <v>99</v>
+      </c>
       <c r="O25" s="21"/>
       <c r="P25" s="21"/>
       <c r="Q25" s="21"/>
@@ -20583,7 +20889,7 @@
         <v>22</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="G26" s="22" t="s">
         <v>91</v>
@@ -20594,11 +20900,15 @@
       <c r="I26" s="22">
         <v>1</v>
       </c>
-      <c r="J26" s="21"/>
+      <c r="J26" s="21" t="s">
+        <v>98</v>
+      </c>
       <c r="K26" s="21"/>
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
-      <c r="N26" s="21"/>
+      <c r="N26" s="21" t="s">
+        <v>99</v>
+      </c>
       <c r="O26" s="21"/>
       <c r="P26" s="21"/>
       <c r="Q26" s="21"/>
@@ -20620,7 +20930,7 @@
         <v>22</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="G27" s="22" t="s">
         <v>91</v>
@@ -20631,11 +20941,15 @@
       <c r="I27" s="22">
         <v>1</v>
       </c>
-      <c r="J27" s="21"/>
+      <c r="J27" s="21" t="s">
+        <v>100</v>
+      </c>
       <c r="K27" s="21"/>
       <c r="L27" s="21"/>
       <c r="M27" s="21"/>
-      <c r="N27" s="21"/>
+      <c r="N27" s="21" t="s">
+        <v>101</v>
+      </c>
       <c r="O27" s="21"/>
       <c r="P27" s="21"/>
       <c r="Q27" s="21"/>
@@ -20657,7 +20971,7 @@
         <v>22</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="G28" s="22" t="s">
         <v>91</v>
@@ -20668,11 +20982,15 @@
       <c r="I28" s="22">
         <v>1</v>
       </c>
-      <c r="J28" s="21"/>
+      <c r="J28" s="21" t="s">
+        <v>100</v>
+      </c>
       <c r="K28" s="21"/>
       <c r="L28" s="21"/>
       <c r="M28" s="21"/>
-      <c r="N28" s="21"/>
+      <c r="N28" s="21" t="s">
+        <v>101</v>
+      </c>
       <c r="O28" s="21"/>
       <c r="P28" s="21"/>
       <c r="Q28" s="21"/>
@@ -20694,7 +21012,7 @@
         <v>22</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="G29" s="22" t="s">
         <v>91</v>
@@ -20705,11 +21023,15 @@
       <c r="I29" s="22">
         <v>1</v>
       </c>
-      <c r="J29" s="21"/>
+      <c r="J29" s="21" t="s">
+        <v>102</v>
+      </c>
       <c r="K29" s="21"/>
       <c r="L29" s="21"/>
       <c r="M29" s="21"/>
-      <c r="N29" s="21"/>
+      <c r="N29" s="21" t="s">
+        <v>103</v>
+      </c>
       <c r="O29" s="21"/>
       <c r="P29" s="21"/>
       <c r="Q29" s="21"/>
@@ -20731,7 +21053,7 @@
         <v>22</v>
       </c>
       <c r="F30" s="22" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="G30" s="22" t="s">
         <v>91</v>
@@ -20742,11 +21064,15 @@
       <c r="I30" s="22">
         <v>1</v>
       </c>
-      <c r="J30" s="21"/>
+      <c r="J30" s="21" t="s">
+        <v>102</v>
+      </c>
       <c r="K30" s="21"/>
       <c r="L30" s="21"/>
       <c r="M30" s="21"/>
-      <c r="N30" s="21"/>
+      <c r="N30" s="21" t="s">
+        <v>103</v>
+      </c>
       <c r="O30" s="21"/>
       <c r="P30" s="21"/>
       <c r="Q30" s="21"/>
@@ -20821,22 +21147,22 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="E1" s="24" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="G1" s="24" t="s">
         <v>3</v>
@@ -20900,11 +21226,15 @@
       <c r="I2" s="22">
         <v>1</v>
       </c>
-      <c r="J2" s="21"/>
+      <c r="J2" s="21" t="s">
+        <v>174</v>
+      </c>
       <c r="K2" s="21"/>
       <c r="L2" s="21"/>
       <c r="M2" s="21"/>
-      <c r="N2" s="21"/>
+      <c r="N2" s="21" t="s">
+        <v>175</v>
+      </c>
       <c r="O2" s="21"/>
       <c r="P2" s="21"/>
       <c r="Q2" s="21"/>
@@ -20937,11 +21267,15 @@
       <c r="I3" s="22">
         <v>1</v>
       </c>
-      <c r="J3" s="21"/>
+      <c r="J3" s="21" t="s">
+        <v>174</v>
+      </c>
       <c r="K3" s="21"/>
       <c r="L3" s="21"/>
       <c r="M3" s="21"/>
-      <c r="N3" s="21"/>
+      <c r="N3" s="21" t="s">
+        <v>175</v>
+      </c>
       <c r="O3" s="21"/>
       <c r="P3" s="21"/>
       <c r="Q3" s="21"/>
@@ -20974,11 +21308,15 @@
       <c r="I4" s="22">
         <v>1</v>
       </c>
-      <c r="J4" s="21"/>
+      <c r="J4" s="21" t="s">
+        <v>92</v>
+      </c>
       <c r="K4" s="21"/>
       <c r="L4" s="21"/>
       <c r="M4" s="21"/>
-      <c r="N4" s="21"/>
+      <c r="N4" s="21" t="s">
+        <v>93</v>
+      </c>
       <c r="O4" s="21"/>
       <c r="P4" s="21"/>
       <c r="Q4" s="21"/>
@@ -21011,11 +21349,15 @@
       <c r="I5" s="22">
         <v>1</v>
       </c>
-      <c r="J5" s="21"/>
+      <c r="J5" s="21" t="s">
+        <v>92</v>
+      </c>
       <c r="K5" s="21"/>
       <c r="L5" s="21"/>
       <c r="M5" s="21"/>
-      <c r="N5" s="21"/>
+      <c r="N5" s="21" t="s">
+        <v>93</v>
+      </c>
       <c r="O5" s="21"/>
       <c r="P5" s="21"/>
       <c r="Q5" s="21"/>
@@ -21037,7 +21379,7 @@
         <v>14</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="G6" s="22" t="s">
         <v>91</v>
@@ -21048,11 +21390,15 @@
       <c r="I6" s="22">
         <v>1</v>
       </c>
-      <c r="J6" s="21"/>
+      <c r="J6" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="K6" s="21"/>
       <c r="L6" s="21"/>
       <c r="M6" s="21"/>
-      <c r="N6" s="21"/>
+      <c r="N6" s="21" t="s">
+        <v>95</v>
+      </c>
       <c r="O6" s="21"/>
       <c r="P6" s="21"/>
       <c r="Q6" s="21"/>
@@ -21077,7 +21423,7 @@
         <v>26</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="H7" s="22">
         <v>0</v>
@@ -21127,7 +21473,7 @@
         <v>22</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="G8" s="22" t="s">
         <v>91</v>
@@ -21138,11 +21484,15 @@
       <c r="I8" s="22">
         <v>1</v>
       </c>
-      <c r="J8" s="21"/>
+      <c r="J8" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="K8" s="21"/>
       <c r="L8" s="21"/>
       <c r="M8" s="21"/>
-      <c r="N8" s="21"/>
+      <c r="N8" s="21" t="s">
+        <v>95</v>
+      </c>
       <c r="O8" s="21"/>
       <c r="P8" s="21"/>
       <c r="Q8" s="21"/>
@@ -21167,7 +21517,7 @@
         <v>32</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="H9" s="22">
         <v>0</v>
@@ -21217,7 +21567,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="G10" s="22" t="s">
         <v>91</v>
@@ -21228,11 +21578,15 @@
       <c r="I10" s="22">
         <v>1</v>
       </c>
-      <c r="J10" s="21"/>
+      <c r="J10" s="21" t="s">
+        <v>96</v>
+      </c>
       <c r="K10" s="21"/>
       <c r="L10" s="21"/>
       <c r="M10" s="21"/>
-      <c r="N10" s="21"/>
+      <c r="N10" s="21" t="s">
+        <v>97</v>
+      </c>
       <c r="O10" s="21"/>
       <c r="P10" s="21"/>
       <c r="Q10" s="21"/>
@@ -21254,7 +21608,7 @@
         <v>22</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="G11" s="22" t="s">
         <v>91</v>
@@ -21265,11 +21619,15 @@
       <c r="I11" s="22">
         <v>1</v>
       </c>
-      <c r="J11" s="21"/>
+      <c r="J11" s="21" t="s">
+        <v>96</v>
+      </c>
       <c r="K11" s="21"/>
       <c r="L11" s="21"/>
       <c r="M11" s="21"/>
-      <c r="N11" s="21"/>
+      <c r="N11" s="21" t="s">
+        <v>97</v>
+      </c>
       <c r="O11" s="21"/>
       <c r="P11" s="21"/>
       <c r="Q11" s="21"/>
@@ -21294,7 +21652,7 @@
         <v>43</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="H12" s="22">
         <v>1</v>
@@ -21341,13 +21699,13 @@
         <v>50</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="F13" s="22" t="s">
         <v>17</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="H13" s="22">
         <v>0</v>
@@ -21355,11 +21713,15 @@
       <c r="I13" s="22">
         <v>1</v>
       </c>
-      <c r="J13" s="21"/>
+      <c r="J13" s="21" t="s">
+        <v>98</v>
+      </c>
       <c r="K13" s="21"/>
       <c r="L13" s="21"/>
       <c r="M13" s="21"/>
-      <c r="N13" s="21"/>
+      <c r="N13" s="21" t="s">
+        <v>99</v>
+      </c>
       <c r="O13" s="21"/>
       <c r="P13" s="21"/>
       <c r="Q13" s="21"/>
@@ -21384,7 +21746,7 @@
         <v>17</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="H14" s="22">
         <v>0</v>
@@ -21392,11 +21754,15 @@
       <c r="I14" s="22">
         <v>1</v>
       </c>
-      <c r="J14" s="21"/>
+      <c r="J14" s="21" t="s">
+        <v>98</v>
+      </c>
       <c r="K14" s="21"/>
       <c r="L14" s="21"/>
       <c r="M14" s="21"/>
-      <c r="N14" s="21"/>
+      <c r="N14" s="21" t="s">
+        <v>99</v>
+      </c>
       <c r="O14" s="21"/>
       <c r="P14" s="21"/>
       <c r="Q14" s="21"/>
@@ -21421,7 +21787,7 @@
         <v>57</v>
       </c>
       <c r="G15" s="22" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="H15" s="22">
         <v>0</v>
@@ -21429,11 +21795,15 @@
       <c r="I15" s="22">
         <v>1</v>
       </c>
-      <c r="J15" s="21"/>
+      <c r="J15" s="21" t="s">
+        <v>100</v>
+      </c>
       <c r="K15" s="21"/>
       <c r="L15" s="21"/>
       <c r="M15" s="21"/>
-      <c r="N15" s="21"/>
+      <c r="N15" s="21" t="s">
+        <v>101</v>
+      </c>
       <c r="O15" s="21"/>
       <c r="P15" s="21"/>
       <c r="Q15" s="21"/>
@@ -21458,7 +21828,7 @@
         <v>57</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="H16" s="22">
         <v>0</v>
@@ -21466,11 +21836,15 @@
       <c r="I16" s="22">
         <v>1</v>
       </c>
-      <c r="J16" s="21"/>
+      <c r="J16" s="21" t="s">
+        <v>100</v>
+      </c>
       <c r="K16" s="21"/>
       <c r="L16" s="21"/>
       <c r="M16" s="21"/>
-      <c r="N16" s="21"/>
+      <c r="N16" s="21" t="s">
+        <v>101</v>
+      </c>
       <c r="O16" s="21"/>
       <c r="P16" s="21"/>
       <c r="Q16" s="21"/>
@@ -21492,10 +21866,10 @@
         <v>14</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="H17" s="22">
         <v>0</v>
@@ -21503,11 +21877,15 @@
       <c r="I17" s="22">
         <v>1</v>
       </c>
-      <c r="J17" s="21"/>
+      <c r="J17" s="21" t="s">
+        <v>102</v>
+      </c>
       <c r="K17" s="21"/>
       <c r="L17" s="21"/>
       <c r="M17" s="21"/>
-      <c r="N17" s="21"/>
+      <c r="N17" s="21" t="s">
+        <v>103</v>
+      </c>
       <c r="O17" s="21"/>
       <c r="P17" s="21"/>
       <c r="Q17" s="21"/>
@@ -21529,7 +21907,7 @@
         <v>22</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="G18" s="22" t="s">
         <v>91</v>
@@ -21540,11 +21918,15 @@
       <c r="I18" s="22">
         <v>1</v>
       </c>
-      <c r="J18" s="21"/>
+      <c r="J18" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="K18" s="21"/>
       <c r="L18" s="21"/>
       <c r="M18" s="21"/>
-      <c r="N18" s="21"/>
+      <c r="N18" s="21" t="s">
+        <v>95</v>
+      </c>
       <c r="O18" s="21"/>
       <c r="P18" s="21"/>
       <c r="Q18" s="21"/>
@@ -21569,7 +21951,7 @@
         <v>26</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="H19" s="22">
         <v>0</v>
@@ -21619,7 +22001,7 @@
         <v>22</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="G20" s="22" t="s">
         <v>91</v>
@@ -21630,11 +22012,15 @@
       <c r="I20" s="22">
         <v>1</v>
       </c>
-      <c r="J20" s="21"/>
+      <c r="J20" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="K20" s="21"/>
       <c r="L20" s="21"/>
       <c r="M20" s="21"/>
-      <c r="N20" s="21"/>
+      <c r="N20" s="21" t="s">
+        <v>95</v>
+      </c>
       <c r="O20" s="21"/>
       <c r="P20" s="21"/>
       <c r="Q20" s="21"/>
@@ -21659,7 +22045,7 @@
         <v>32</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="H21" s="22">
         <v>0</v>
@@ -21709,7 +22095,7 @@
         <v>22</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="G22" s="22" t="s">
         <v>91</v>
@@ -21720,11 +22106,15 @@
       <c r="I22" s="22">
         <v>1</v>
       </c>
-      <c r="J22" s="21"/>
+      <c r="J22" s="21" t="s">
+        <v>96</v>
+      </c>
       <c r="K22" s="21"/>
       <c r="L22" s="21"/>
       <c r="M22" s="21"/>
-      <c r="N22" s="21"/>
+      <c r="N22" s="21" t="s">
+        <v>97</v>
+      </c>
       <c r="O22" s="21"/>
       <c r="P22" s="21"/>
       <c r="Q22" s="21"/>
@@ -21746,7 +22136,7 @@
         <v>22</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="G23" s="22" t="s">
         <v>91</v>
@@ -21757,11 +22147,15 @@
       <c r="I23" s="22">
         <v>1</v>
       </c>
-      <c r="J23" s="21"/>
+      <c r="J23" s="21" t="s">
+        <v>96</v>
+      </c>
       <c r="K23" s="21"/>
       <c r="L23" s="21"/>
       <c r="M23" s="21"/>
-      <c r="N23" s="21"/>
+      <c r="N23" s="21" t="s">
+        <v>97</v>
+      </c>
       <c r="O23" s="21"/>
       <c r="P23" s="21"/>
       <c r="Q23" s="21"/>
@@ -21786,7 +22180,7 @@
         <v>43</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="H24" s="22">
         <v>1</v>
@@ -21839,7 +22233,7 @@
         <v>17</v>
       </c>
       <c r="G25" s="22" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="H25" s="22">
         <v>0</v>
@@ -21847,11 +22241,15 @@
       <c r="I25" s="22">
         <v>1</v>
       </c>
-      <c r="J25" s="21"/>
+      <c r="J25" s="21" t="s">
+        <v>98</v>
+      </c>
       <c r="K25" s="21"/>
       <c r="L25" s="21"/>
       <c r="M25" s="21"/>
-      <c r="N25" s="21"/>
+      <c r="N25" s="21" t="s">
+        <v>99</v>
+      </c>
       <c r="O25" s="21"/>
       <c r="P25" s="21"/>
       <c r="Q25" s="21"/>
@@ -21876,7 +22274,7 @@
         <v>17</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="H26" s="22">
         <v>0</v>
@@ -21884,11 +22282,15 @@
       <c r="I26" s="22">
         <v>1</v>
       </c>
-      <c r="J26" s="21"/>
+      <c r="J26" s="21" t="s">
+        <v>98</v>
+      </c>
       <c r="K26" s="21"/>
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
-      <c r="N26" s="21"/>
+      <c r="N26" s="21" t="s">
+        <v>99</v>
+      </c>
       <c r="O26" s="21"/>
       <c r="P26" s="21"/>
       <c r="Q26" s="21"/>
@@ -21913,7 +22315,7 @@
         <v>57</v>
       </c>
       <c r="G27" s="22" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="H27" s="22">
         <v>0</v>
@@ -21921,11 +22323,15 @@
       <c r="I27" s="22">
         <v>1</v>
       </c>
-      <c r="J27" s="21"/>
+      <c r="J27" s="21" t="s">
+        <v>100</v>
+      </c>
       <c r="K27" s="21"/>
       <c r="L27" s="21"/>
       <c r="M27" s="21"/>
-      <c r="N27" s="21"/>
+      <c r="N27" s="21" t="s">
+        <v>101</v>
+      </c>
       <c r="O27" s="21"/>
       <c r="P27" s="21"/>
       <c r="Q27" s="21"/>
@@ -21950,7 +22356,7 @@
         <v>57</v>
       </c>
       <c r="G28" s="22" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="H28" s="22">
         <v>0</v>
@@ -21958,11 +22364,15 @@
       <c r="I28" s="22">
         <v>1</v>
       </c>
-      <c r="J28" s="21"/>
+      <c r="J28" s="21" t="s">
+        <v>100</v>
+      </c>
       <c r="K28" s="21"/>
       <c r="L28" s="21"/>
       <c r="M28" s="21"/>
-      <c r="N28" s="21"/>
+      <c r="N28" s="21" t="s">
+        <v>101</v>
+      </c>
       <c r="O28" s="21"/>
       <c r="P28" s="21"/>
       <c r="Q28" s="21"/>
@@ -21984,10 +22394,10 @@
         <v>22</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="G29" s="22" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="H29" s="22">
         <v>0</v>
@@ -21995,11 +22405,15 @@
       <c r="I29" s="22">
         <v>1</v>
       </c>
-      <c r="J29" s="21"/>
+      <c r="J29" s="21" t="s">
+        <v>102</v>
+      </c>
       <c r="K29" s="21"/>
       <c r="L29" s="21"/>
       <c r="M29" s="21"/>
-      <c r="N29" s="21"/>
+      <c r="N29" s="21" t="s">
+        <v>103</v>
+      </c>
       <c r="O29" s="21"/>
       <c r="P29" s="21"/>
       <c r="Q29" s="21"/>
@@ -22021,10 +22435,10 @@
         <v>22</v>
       </c>
       <c r="F30" s="22" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="G30" s="22" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="H30" s="22">
         <v>0</v>
@@ -22032,11 +22446,15 @@
       <c r="I30" s="22">
         <v>1</v>
       </c>
-      <c r="J30" s="21"/>
+      <c r="J30" s="21" t="s">
+        <v>102</v>
+      </c>
       <c r="K30" s="21"/>
       <c r="L30" s="21"/>
       <c r="M30" s="21"/>
-      <c r="N30" s="21"/>
+      <c r="N30" s="21" t="s">
+        <v>103</v>
+      </c>
       <c r="O30" s="21"/>
       <c r="P30" s="21"/>
       <c r="Q30" s="21"/>
@@ -22111,22 +22529,22 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="E1" s="24" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="G1" s="24" t="s">
         <v>3</v>
@@ -22190,11 +22608,15 @@
       <c r="I2" s="22">
         <v>1</v>
       </c>
-      <c r="J2" s="21"/>
+      <c r="J2" s="21" t="s">
+        <v>174</v>
+      </c>
       <c r="K2" s="21"/>
       <c r="L2" s="21"/>
       <c r="M2" s="21"/>
-      <c r="N2" s="21"/>
+      <c r="N2" s="21" t="s">
+        <v>175</v>
+      </c>
       <c r="O2" s="21"/>
       <c r="P2" s="21"/>
       <c r="Q2" s="21"/>
@@ -22227,11 +22649,15 @@
       <c r="I3" s="22">
         <v>1</v>
       </c>
-      <c r="J3" s="21"/>
+      <c r="J3" s="21" t="s">
+        <v>174</v>
+      </c>
       <c r="K3" s="21"/>
       <c r="L3" s="21"/>
       <c r="M3" s="21"/>
-      <c r="N3" s="21"/>
+      <c r="N3" s="21" t="s">
+        <v>175</v>
+      </c>
       <c r="O3" s="21"/>
       <c r="P3" s="21"/>
       <c r="Q3" s="21"/>
@@ -22256,7 +22682,7 @@
         <v>26</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="H4" s="22">
         <v>0</v>
@@ -22264,11 +22690,15 @@
       <c r="I4" s="22">
         <v>1</v>
       </c>
-      <c r="J4" s="21"/>
+      <c r="J4" s="21" t="s">
+        <v>92</v>
+      </c>
       <c r="K4" s="21"/>
       <c r="L4" s="21"/>
       <c r="M4" s="21"/>
-      <c r="N4" s="21"/>
+      <c r="N4" s="21" t="s">
+        <v>93</v>
+      </c>
       <c r="O4" s="21"/>
       <c r="P4" s="21"/>
       <c r="Q4" s="21"/>
@@ -22293,7 +22723,7 @@
         <v>26</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="H5" s="22">
         <v>0</v>
@@ -22301,11 +22731,15 @@
       <c r="I5" s="22">
         <v>1</v>
       </c>
-      <c r="J5" s="21"/>
+      <c r="J5" s="21" t="s">
+        <v>92</v>
+      </c>
       <c r="K5" s="21"/>
       <c r="L5" s="21"/>
       <c r="M5" s="21"/>
-      <c r="N5" s="21"/>
+      <c r="N5" s="21" t="s">
+        <v>93</v>
+      </c>
       <c r="O5" s="21"/>
       <c r="P5" s="21"/>
       <c r="Q5" s="21"/>
@@ -22330,7 +22764,7 @@
         <v>32</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="H6" s="22">
         <v>0</v>
@@ -22338,11 +22772,15 @@
       <c r="I6" s="22">
         <v>1</v>
       </c>
-      <c r="J6" s="21"/>
+      <c r="J6" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="K6" s="21"/>
       <c r="L6" s="21"/>
       <c r="M6" s="21"/>
-      <c r="N6" s="21"/>
+      <c r="N6" s="21" t="s">
+        <v>95</v>
+      </c>
       <c r="O6" s="21"/>
       <c r="P6" s="21"/>
       <c r="Q6" s="21"/>
@@ -22367,7 +22805,7 @@
         <v>43</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="H7" s="22">
         <v>0</v>
@@ -22420,7 +22858,7 @@
         <v>32</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="H8" s="22">
         <v>0</v>
@@ -22428,11 +22866,15 @@
       <c r="I8" s="22">
         <v>1</v>
       </c>
-      <c r="J8" s="21"/>
+      <c r="J8" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="K8" s="21"/>
       <c r="L8" s="21"/>
       <c r="M8" s="21"/>
-      <c r="N8" s="21"/>
+      <c r="N8" s="21" t="s">
+        <v>95</v>
+      </c>
       <c r="O8" s="21"/>
       <c r="P8" s="21"/>
       <c r="Q8" s="21"/>
@@ -22457,7 +22899,7 @@
         <v>51</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="H9" s="22">
         <v>0</v>
@@ -22510,7 +22952,7 @@
         <v>57</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="H10" s="22">
         <v>0</v>
@@ -22518,11 +22960,15 @@
       <c r="I10" s="22">
         <v>1</v>
       </c>
-      <c r="J10" s="21"/>
+      <c r="J10" s="21" t="s">
+        <v>96</v>
+      </c>
       <c r="K10" s="21"/>
       <c r="L10" s="21"/>
       <c r="M10" s="21"/>
-      <c r="N10" s="21"/>
+      <c r="N10" s="21" t="s">
+        <v>97</v>
+      </c>
       <c r="O10" s="21"/>
       <c r="P10" s="21"/>
       <c r="Q10" s="21"/>
@@ -22547,7 +22993,7 @@
         <v>57</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="H11" s="22">
         <v>0</v>
@@ -22555,11 +23001,15 @@
       <c r="I11" s="22">
         <v>1</v>
       </c>
-      <c r="J11" s="21"/>
+      <c r="J11" s="21" t="s">
+        <v>96</v>
+      </c>
       <c r="K11" s="21"/>
       <c r="L11" s="21"/>
       <c r="M11" s="21"/>
-      <c r="N11" s="21"/>
+      <c r="N11" s="21" t="s">
+        <v>97</v>
+      </c>
       <c r="O11" s="21"/>
       <c r="P11" s="21"/>
       <c r="Q11" s="21"/>
@@ -22584,7 +23034,7 @@
         <v>63</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="H12" s="22">
         <v>1</v>
@@ -22634,7 +23084,7 @@
         <v>14</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="G13" s="22" t="s">
         <v>21</v>
@@ -22645,11 +23095,15 @@
       <c r="I13" s="22">
         <v>1</v>
       </c>
-      <c r="J13" s="21"/>
+      <c r="J13" s="21" t="s">
+        <v>98</v>
+      </c>
       <c r="K13" s="21"/>
       <c r="L13" s="21"/>
       <c r="M13" s="21"/>
-      <c r="N13" s="21"/>
+      <c r="N13" s="21" t="s">
+        <v>99</v>
+      </c>
       <c r="O13" s="21"/>
       <c r="P13" s="21"/>
       <c r="Q13" s="21"/>
@@ -22671,7 +23125,7 @@
         <v>22</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="G14" s="22" t="s">
         <v>21</v>
@@ -22682,11 +23136,15 @@
       <c r="I14" s="22">
         <v>1</v>
       </c>
-      <c r="J14" s="21"/>
+      <c r="J14" s="21" t="s">
+        <v>98</v>
+      </c>
       <c r="K14" s="21"/>
       <c r="L14" s="21"/>
       <c r="M14" s="21"/>
-      <c r="N14" s="21"/>
+      <c r="N14" s="21" t="s">
+        <v>99</v>
+      </c>
       <c r="O14" s="21"/>
       <c r="P14" s="21"/>
       <c r="Q14" s="21"/>
@@ -22708,10 +23166,10 @@
         <v>14</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="G15" s="22" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="H15" s="22">
         <v>0</v>
@@ -22719,11 +23177,15 @@
       <c r="I15" s="22">
         <v>1</v>
       </c>
-      <c r="J15" s="21"/>
+      <c r="J15" s="21" t="s">
+        <v>100</v>
+      </c>
       <c r="K15" s="21"/>
       <c r="L15" s="21"/>
       <c r="M15" s="21"/>
-      <c r="N15" s="21"/>
+      <c r="N15" s="21" t="s">
+        <v>101</v>
+      </c>
       <c r="O15" s="21"/>
       <c r="P15" s="21"/>
       <c r="Q15" s="21"/>
@@ -22745,10 +23207,10 @@
         <v>22</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="H16" s="22">
         <v>0</v>
@@ -22756,11 +23218,15 @@
       <c r="I16" s="22">
         <v>1</v>
       </c>
-      <c r="J16" s="21"/>
+      <c r="J16" s="21" t="s">
+        <v>100</v>
+      </c>
       <c r="K16" s="21"/>
       <c r="L16" s="21"/>
       <c r="M16" s="21"/>
-      <c r="N16" s="21"/>
+      <c r="N16" s="21" t="s">
+        <v>101</v>
+      </c>
       <c r="O16" s="21"/>
       <c r="P16" s="21"/>
       <c r="Q16" s="21"/>
@@ -22782,10 +23248,10 @@
         <v>14</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="H17" s="22">
         <v>0</v>
@@ -22793,11 +23259,15 @@
       <c r="I17" s="22">
         <v>1</v>
       </c>
-      <c r="J17" s="21"/>
+      <c r="J17" s="21" t="s">
+        <v>102</v>
+      </c>
       <c r="K17" s="21"/>
       <c r="L17" s="21"/>
       <c r="M17" s="21"/>
-      <c r="N17" s="21"/>
+      <c r="N17" s="21" t="s">
+        <v>103</v>
+      </c>
       <c r="O17" s="21"/>
       <c r="P17" s="21"/>
       <c r="Q17" s="21"/>
@@ -22822,7 +23292,7 @@
         <v>32</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="H18" s="22">
         <v>0</v>
@@ -22830,11 +23300,15 @@
       <c r="I18" s="22">
         <v>1</v>
       </c>
-      <c r="J18" s="21"/>
+      <c r="J18" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="K18" s="21"/>
       <c r="L18" s="21"/>
       <c r="M18" s="21"/>
-      <c r="N18" s="21"/>
+      <c r="N18" s="21" t="s">
+        <v>95</v>
+      </c>
       <c r="O18" s="21"/>
       <c r="P18" s="21"/>
       <c r="Q18" s="21"/>
@@ -22859,7 +23333,7 @@
         <v>43</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="H19" s="22">
         <v>0</v>
@@ -22912,7 +23386,7 @@
         <v>32</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="H20" s="22">
         <v>0</v>
@@ -22920,11 +23394,15 @@
       <c r="I20" s="22">
         <v>1</v>
       </c>
-      <c r="J20" s="21"/>
+      <c r="J20" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="K20" s="21"/>
       <c r="L20" s="21"/>
       <c r="M20" s="21"/>
-      <c r="N20" s="21"/>
+      <c r="N20" s="21" t="s">
+        <v>95</v>
+      </c>
       <c r="O20" s="21"/>
       <c r="P20" s="21"/>
       <c r="Q20" s="21"/>
@@ -22949,7 +23427,7 @@
         <v>51</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="H21" s="22">
         <v>0</v>
@@ -23002,7 +23480,7 @@
         <v>57</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="H22" s="22">
         <v>0</v>
@@ -23010,11 +23488,15 @@
       <c r="I22" s="22">
         <v>1</v>
       </c>
-      <c r="J22" s="21"/>
+      <c r="J22" s="21" t="s">
+        <v>96</v>
+      </c>
       <c r="K22" s="21"/>
       <c r="L22" s="21"/>
       <c r="M22" s="21"/>
-      <c r="N22" s="21"/>
+      <c r="N22" s="21" t="s">
+        <v>97</v>
+      </c>
       <c r="O22" s="21"/>
       <c r="P22" s="21"/>
       <c r="Q22" s="21"/>
@@ -23039,7 +23521,7 @@
         <v>57</v>
       </c>
       <c r="G23" s="22" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="H23" s="22">
         <v>0</v>
@@ -23047,11 +23529,15 @@
       <c r="I23" s="22">
         <v>1</v>
       </c>
-      <c r="J23" s="21"/>
+      <c r="J23" s="21" t="s">
+        <v>96</v>
+      </c>
       <c r="K23" s="21"/>
       <c r="L23" s="21"/>
       <c r="M23" s="21"/>
-      <c r="N23" s="21"/>
+      <c r="N23" s="21" t="s">
+        <v>97</v>
+      </c>
       <c r="O23" s="21"/>
       <c r="P23" s="21"/>
       <c r="Q23" s="21"/>
@@ -23076,7 +23562,7 @@
         <v>63</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="H24" s="22">
         <v>1</v>
@@ -23126,7 +23612,7 @@
         <v>22</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="G25" s="22" t="s">
         <v>21</v>
@@ -23137,11 +23623,15 @@
       <c r="I25" s="22">
         <v>1</v>
       </c>
-      <c r="J25" s="21"/>
+      <c r="J25" s="21" t="s">
+        <v>98</v>
+      </c>
       <c r="K25" s="21"/>
       <c r="L25" s="21"/>
       <c r="M25" s="21"/>
-      <c r="N25" s="21"/>
+      <c r="N25" s="21" t="s">
+        <v>99</v>
+      </c>
       <c r="O25" s="21"/>
       <c r="P25" s="21"/>
       <c r="Q25" s="21"/>
@@ -23163,7 +23653,7 @@
         <v>22</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="G26" s="22" t="s">
         <v>21</v>
@@ -23174,11 +23664,15 @@
       <c r="I26" s="22">
         <v>1</v>
       </c>
-      <c r="J26" s="21"/>
+      <c r="J26" s="21" t="s">
+        <v>98</v>
+      </c>
       <c r="K26" s="21"/>
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
-      <c r="N26" s="21"/>
+      <c r="N26" s="21" t="s">
+        <v>99</v>
+      </c>
       <c r="O26" s="21"/>
       <c r="P26" s="21"/>
       <c r="Q26" s="21"/>
@@ -23200,10 +23694,10 @@
         <v>22</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="G27" s="22" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="H27" s="22">
         <v>0</v>
@@ -23211,11 +23705,15 @@
       <c r="I27" s="22">
         <v>1</v>
       </c>
-      <c r="J27" s="21"/>
+      <c r="J27" s="21" t="s">
+        <v>100</v>
+      </c>
       <c r="K27" s="21"/>
       <c r="L27" s="21"/>
       <c r="M27" s="21"/>
-      <c r="N27" s="21"/>
+      <c r="N27" s="21" t="s">
+        <v>101</v>
+      </c>
       <c r="O27" s="21"/>
       <c r="P27" s="21"/>
       <c r="Q27" s="21"/>
@@ -23237,10 +23735,10 @@
         <v>22</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="G28" s="22" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="H28" s="22">
         <v>0</v>
@@ -23248,11 +23746,15 @@
       <c r="I28" s="22">
         <v>1</v>
       </c>
-      <c r="J28" s="21"/>
+      <c r="J28" s="21" t="s">
+        <v>100</v>
+      </c>
       <c r="K28" s="21"/>
       <c r="L28" s="21"/>
       <c r="M28" s="21"/>
-      <c r="N28" s="21"/>
+      <c r="N28" s="21" t="s">
+        <v>101</v>
+      </c>
       <c r="O28" s="21"/>
       <c r="P28" s="21"/>
       <c r="Q28" s="21"/>
@@ -23274,10 +23776,10 @@
         <v>22</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="G29" s="22" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="H29" s="22">
         <v>0</v>
@@ -23285,11 +23787,15 @@
       <c r="I29" s="22">
         <v>1</v>
       </c>
-      <c r="J29" s="21"/>
+      <c r="J29" s="21" t="s">
+        <v>102</v>
+      </c>
       <c r="K29" s="21"/>
       <c r="L29" s="21"/>
       <c r="M29" s="21"/>
-      <c r="N29" s="21"/>
+      <c r="N29" s="21" t="s">
+        <v>103</v>
+      </c>
       <c r="O29" s="21"/>
       <c r="P29" s="21"/>
       <c r="Q29" s="21"/>
@@ -23311,10 +23817,10 @@
         <v>22</v>
       </c>
       <c r="F30" s="22" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="G30" s="22" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="H30" s="22">
         <v>0</v>
@@ -23322,11 +23828,15 @@
       <c r="I30" s="22">
         <v>1</v>
       </c>
-      <c r="J30" s="21"/>
+      <c r="J30" s="21" t="s">
+        <v>102</v>
+      </c>
       <c r="K30" s="21"/>
       <c r="L30" s="21"/>
       <c r="M30" s="21"/>
-      <c r="N30" s="21"/>
+      <c r="N30" s="21" t="s">
+        <v>103</v>
+      </c>
       <c r="O30" s="21"/>
       <c r="P30" s="21"/>
       <c r="Q30" s="21"/>
@@ -23397,34 +23907,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="E1" s="24" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="H1" s="24" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="I1" s="24" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="J1" s="24" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -23432,10 +23942,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="D2" s="22" t="s">
         <v>13</v>
@@ -23575,7 +24085,7 @@
         <v>47</v>
       </c>
       <c r="G6" s="27" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="H6" s="22" t="s">
         <v>13</v>
@@ -23607,10 +24117,10 @@
         <v>47</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I7" s="22" t="s">
         <v>13</v>
@@ -23639,13 +24149,13 @@
         <v>47</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I8" s="27" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="J8" s="22" t="s">
         <v>13</v>
@@ -23671,16 +24181,16 @@
         <v>47</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="J9" s="27" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -23703,16 +24213,16 @@
         <v>47</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I10" s="22" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -23735,16 +24245,16 @@
         <v>47</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I11" s="22" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="J11" s="22" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -23767,16 +24277,16 @@
         <v>47</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I12" s="22" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -23799,16 +24309,16 @@
         <v>70</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="H13" s="22" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I13" s="22" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="J13" s="22" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -23831,16 +24341,16 @@
         <v>70</v>
       </c>
       <c r="G14" s="27" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I14" s="22" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="J14" s="22" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -23863,16 +24373,16 @@
         <v>70</v>
       </c>
       <c r="G15" s="22" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I15" s="22" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="J15" s="22" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -23895,16 +24405,16 @@
         <v>70</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="H16" s="27" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="I16" s="22" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="J16" s="22" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -23927,16 +24437,16 @@
         <v>70</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="H17" s="22" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="I17" s="27" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="J17" s="22" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -23959,16 +24469,16 @@
         <v>70</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="J18" s="27" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -23991,16 +24501,16 @@
         <v>70</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="I19" s="22" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -24014,7 +24524,7 @@
         <v>49</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="E20" s="22" t="s">
         <v>68</v>
@@ -24023,16 +24533,16 @@
         <v>70</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="I20" s="22" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="J20" s="22" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -24046,25 +24556,25 @@
         <v>53</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="F21" s="22" t="s">
         <v>70</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="H21" s="22" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="I21" s="22" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="J21" s="22" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -24078,25 +24588,25 @@
         <v>55</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="F22" s="27" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="H22" s="22" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="I22" s="22" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="J22" s="22" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -24110,25 +24620,25 @@
         <v>59</v>
       </c>
       <c r="D23" s="22" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="G23" s="27" t="s">
         <v>13</v>
       </c>
       <c r="H23" s="22" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="I23" s="22" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="J23" s="22" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -24142,25 +24652,25 @@
         <v>61</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="G24" s="22" t="s">
         <v>13</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="I24" s="22" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="J24" s="22" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -24174,25 +24684,25 @@
         <v>72</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="G25" s="22" t="s">
         <v>13</v>
       </c>
       <c r="H25" s="22" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="I25" s="22" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="J25" s="22" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
